--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEW_JERSEY_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEW_JERSEY_2010.xlsx
@@ -15054,7 +15054,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C817">
@@ -16764,7 +16764,7 @@
       </c>
       <c r="B912" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C912">
